--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123639662</v>
       </c>
       <c r="B3" t="n">
-        <v>58341</v>
+        <v>58347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123639662</v>
       </c>
       <c r="B3" t="n">
-        <v>58347</v>
+        <v>58350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123639662</v>
       </c>
       <c r="B3" t="n">
-        <v>58350</v>
+        <v>58351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>132184191</v>
       </c>
       <c r="B4" t="n">
-        <v>58810</v>
+        <v>58812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>132184124</v>
       </c>
       <c r="B5" t="n">
-        <v>58810</v>
+        <v>58812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>132184191</v>
       </c>
       <c r="B4" t="n">
-        <v>58812</v>
+        <v>58813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>132184124</v>
       </c>
       <c r="B5" t="n">
-        <v>58812</v>
+        <v>58813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>132184191</v>
       </c>
       <c r="B4" t="n">
-        <v>58813</v>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>132184124</v>
       </c>
       <c r="B5" t="n">
-        <v>58813</v>
+        <v>58817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>132184191</v>
       </c>
       <c r="B4" t="n">
-        <v>58817</v>
+        <v>58818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>132184124</v>
       </c>
       <c r="B5" t="n">
-        <v>58817</v>
+        <v>58818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112162570</v>
       </c>
       <c r="B2" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,7 +721,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356272</v>
+        <v>356271</v>
       </c>
       <c r="R2" t="n">
         <v>6410425</v>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123639662</v>
+        <v>123639641</v>
       </c>
       <c r="B3" t="n">
-        <v>58373</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356451</v>
+        <v>356376</v>
       </c>
       <c r="R3" t="n">
-        <v>6410429</v>
+        <v>6410397</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Utspidda i mindre samlingar längs diket.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132184191</v>
+        <v>123639662</v>
       </c>
       <c r="B4" t="n">
-        <v>58818</v>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,7 +929,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,24 +937,24 @@
           <t>äggklumpar</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ödenäs, Vg</t>
+          <t>Långevik, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>356465</v>
+        <v>356451</v>
       </c>
       <c r="R4" t="n">
-        <v>6410457</v>
+        <v>6410429</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,12 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Utspidda i mindre samlingar längs diket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andrea Albeck</t>
+          <t>Andrea Albeck, Rasmus Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1032,7 +1022,7 @@
         <v>132184124</v>
       </c>
       <c r="B5" t="n">
-        <v>58818</v>
+        <v>58839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,6 +1129,342 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132184150</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ödenäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>356342</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6410411</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ödenäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andrea Albeck</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andrea Albeck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132184191</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ödenäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>356465</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6410457</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ödenäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andrea Albeck</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andrea Albeck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>90145905</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>08C-UWJ, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>356233</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6410403</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ödenäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>GDP Slåtterängar och naturbetesmarker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56053-2023 artfynd.xlsx
+++ b/artfynd/A 56053-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112162570</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123639641</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123639662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132184124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132184150</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132184191</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,8 +1499,22 @@
           <t>GDP Slåtterängar och naturbetesmarker</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90145905</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>